--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/magallanes-y-antartica.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>30033.13</v>
+        <v>29868.97</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5520.31</v>
+        <v>5545.32</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>18938.51</v>
+        <v>18439.8</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>23656.13</v>
+        <v>23022.7</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13975.49</v>
+        <v>14019.97</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10571.52</v>
+        <v>10679.03</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5713.29</v>
+        <v>5725.47</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>35810.32</v>
+        <v>35611.79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2983-178-CM25</t>
+          <t>1960-39-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,43 +569,43 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>29868.97</v>
+        <v>20281.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2348-1647-CM25</t>
+          <t>709129-42-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IDEA MARKET SPA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.148.288-2</t>
+          <t>77.043.435-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5545.32</v>
+        <v>69145.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5338-171-CM26</t>
+          <t>2983-178-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>18439.8</v>
+        <v>29868.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1237328-123-CM26</t>
+          <t>2348-1647-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>IDEA MARKET SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.148.288-2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>23022.7</v>
+        <v>5545.32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5394-255-CM26</t>
+          <t>5338-171-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>14019.97</v>
+        <v>18439.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2348-240-CM26</t>
+          <t>1237328-123-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>10679.03</v>
+        <v>23022.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3866-80-CM26</t>
+          <t>5394-255-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.018.060-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5725.47</v>
+        <v>14019.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5394-432-CM26</t>
+          <t>2348-240-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.018.060-0</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,6 +996,128 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
+        <v>10679.03</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3866-80-CM26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.251.300-2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>5725.47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5394-432-CM26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>71.133.700-8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>35611.79</v>
       </c>
     </row>
